--- a/artfynd/A 36692-2025 artfynd.xlsx
+++ b/artfynd/A 36692-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017294</v>
       </c>
       <c r="B2" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126379685</v>
       </c>
       <c r="B3" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
